--- a/config/配置_创远_EMS.xlsx
+++ b/config/配置_创远_EMS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24771" windowHeight="10748" activeTab="4"/>
+    <workbookView windowWidth="24634" windowHeight="10697" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="158">
   <si>
     <t>key</t>
   </si>
@@ -364,6 +364,84 @@
     <t>bau2</t>
   </si>
   <si>
+    <t>bcu1</t>
+  </si>
+  <si>
+    <t>BCU</t>
+  </si>
+  <si>
+    <t>协能2级BCU</t>
+  </si>
+  <si>
+    <t>bcu2</t>
+  </si>
+  <si>
+    <t>bcu3</t>
+  </si>
+  <si>
+    <t>bcu4</t>
+  </si>
+  <si>
+    <t>bcu5</t>
+  </si>
+  <si>
+    <t>bcu6</t>
+  </si>
+  <si>
+    <t>bcu7</t>
+  </si>
+  <si>
+    <t>bcu8</t>
+  </si>
+  <si>
+    <t>bcu9</t>
+  </si>
+  <si>
+    <t>bcu10</t>
+  </si>
+  <si>
+    <t>bcu11</t>
+  </si>
+  <si>
+    <t>bcu12</t>
+  </si>
+  <si>
+    <t>bcu13</t>
+  </si>
+  <si>
+    <t>bcu14</t>
+  </si>
+  <si>
+    <t>bcu15</t>
+  </si>
+  <si>
+    <t>bcu16</t>
+  </si>
+  <si>
+    <t>bcu17</t>
+  </si>
+  <si>
+    <t>bcu18</t>
+  </si>
+  <si>
+    <t>bcu19</t>
+  </si>
+  <si>
+    <t>bcu20</t>
+  </si>
+  <si>
+    <t>bcu21</t>
+  </si>
+  <si>
+    <t>bcu22</t>
+  </si>
+  <si>
+    <t>bcu23</t>
+  </si>
+  <si>
+    <t>bcu24</t>
+  </si>
+  <si>
     <t>comType</t>
   </si>
   <si>
@@ -419,6 +497,9 @@
   </si>
   <si>
     <t>./config/bms/BAU_协能.xlsx</t>
+  </si>
+  <si>
+    <t>./config/bms/BCU_协能.xlsx</t>
   </si>
   <si>
     <t>device_id</t>
@@ -608,12 +689,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1034,7 +1127,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1058,16 +1151,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1076,89 +1169,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1171,18 +1264,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1201,28 +1303,34 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1599,401 +1707,401 @@
     <col min="8" max="16384" width="9.03100775193798" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="10" customFormat="1" spans="1:7">
+      <c r="A1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="6" customFormat="1" spans="1:7">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="11" customFormat="1" spans="1:7">
+      <c r="A2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="6" t="b">
+      <c r="F2" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="7" customFormat="1" spans="1:7">
-      <c r="A3" s="7" t="s">
+    <row r="3" s="12" customFormat="1" spans="1:7">
+      <c r="A3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="7" t="b">
+      <c r="F3" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" s="7" customFormat="1" spans="1:7">
-      <c r="B4" s="7" t="s">
+    <row r="4" s="12" customFormat="1" spans="1:7">
+      <c r="B4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="12">
         <v>9091</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" s="8" customFormat="1" spans="1:7">
-      <c r="A5" s="8" t="s">
+    <row r="5" s="13" customFormat="1" spans="1:7">
+      <c r="A5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="8" t="b">
+      <c r="F5" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" s="9" customFormat="1" spans="1:7">
-      <c r="A6" s="9" t="s">
+    <row r="6" s="14" customFormat="1" spans="1:7">
+      <c r="A6" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="9" t="b">
+      <c r="F6" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" s="9" customFormat="1" spans="1:7">
-      <c r="B7" s="9" t="s">
+    <row r="7" s="14" customFormat="1" spans="1:7">
+      <c r="B7" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="14">
         <v>9092</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" s="9" customFormat="1" spans="1:7">
-      <c r="B8" s="9" t="s">
+    <row r="8" s="14" customFormat="1" spans="1:7">
+      <c r="B8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" s="10" customFormat="1" spans="1:7">
-      <c r="A9" s="10" t="s">
+    <row r="9" s="15" customFormat="1" spans="1:7">
+      <c r="A9" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="14" t="b">
+      <c r="F9" s="19" t="b">
         <v>1</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="19" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" s="10" customFormat="1" spans="1:7">
-      <c r="B10" s="10" t="s">
+    <row r="10" s="15" customFormat="1" spans="1:7">
+      <c r="B10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="15">
         <v>2404</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-    </row>
-    <row r="11" s="10" customFormat="1" spans="1:7">
-      <c r="B11" s="10" t="s">
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" s="15" customFormat="1" spans="1:7">
+      <c r="B11" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-    </row>
-    <row r="12" s="10" customFormat="1" spans="1:7">
-      <c r="B12" s="10" t="s">
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" s="15" customFormat="1" spans="1:7">
+      <c r="B12" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="15">
         <v>0</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-    </row>
-    <row r="13" s="10" customFormat="1" ht="36.85" spans="1:7">
-      <c r="B13" s="10" t="s">
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" s="15" customFormat="1" ht="36.85" spans="1:7">
+      <c r="B13" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="10" t="b">
+      <c r="C13" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-    </row>
-    <row r="14" s="10" customFormat="1" spans="1:7">
-      <c r="B14" s="10" t="s">
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" s="15" customFormat="1" spans="1:7">
+      <c r="B14" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="15">
         <v>30000</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-    </row>
-    <row r="15" s="10" customFormat="1" ht="36.85" spans="1:7">
-      <c r="B15" s="10" t="s">
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" s="15" customFormat="1" ht="36.85" spans="1:7">
+      <c r="B15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="10" t="b">
+      <c r="C15" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-    </row>
-    <row r="16" s="11" customFormat="1" spans="1:7">
-      <c r="A16" s="18" t="s">
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+    </row>
+    <row r="16" s="16" customFormat="1" spans="1:7">
+      <c r="A16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="19" t="b">
+      <c r="F16" s="24" t="b">
         <v>1</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="24" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" s="11" customFormat="1" spans="1:7">
-      <c r="A17" s="19"/>
-      <c r="B17" s="11" t="s">
+    <row r="17" s="16" customFormat="1" spans="1:7">
+      <c r="A17" s="24"/>
+      <c r="B17" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="16">
         <v>500</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-    </row>
-    <row r="18" s="11" customFormat="1" spans="1:7">
-      <c r="A18" s="19"/>
-      <c r="B18" s="11" t="s">
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+    </row>
+    <row r="18" s="16" customFormat="1" spans="1:7">
+      <c r="A18" s="24"/>
+      <c r="B18" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="16">
         <v>60000</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-    </row>
-    <row r="19" s="11" customFormat="1" spans="1:7">
-      <c r="A19" s="19"/>
-      <c r="B19" s="11" t="s">
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+    </row>
+    <row r="19" s="16" customFormat="1" spans="1:7">
+      <c r="A19" s="24"/>
+      <c r="B19" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="16">
         <v>1</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-    </row>
-    <row r="20" s="11" customFormat="1" spans="1:7">
-      <c r="A20" s="19"/>
-      <c r="B20" s="11" t="s">
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+    </row>
+    <row r="20" s="16" customFormat="1" spans="1:7">
+      <c r="A20" s="24"/>
+      <c r="B20" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="16">
         <v>1</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-    </row>
-    <row r="21" s="11" customFormat="1" ht="36.85" spans="1:7">
-      <c r="A21" s="19"/>
-      <c r="B21" s="11" t="s">
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+    </row>
+    <row r="21" s="16" customFormat="1" ht="36.85" spans="1:7">
+      <c r="A21" s="24"/>
+      <c r="B21" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="20" t="b">
+      <c r="C21" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-    </row>
-    <row r="22" s="12" customFormat="1" spans="1:7">
-      <c r="A22" s="12" t="s">
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+    </row>
+    <row r="22" s="17" customFormat="1" spans="1:7">
+      <c r="A22" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="12" t="b">
+      <c r="F22" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="23" s="13" customFormat="1" spans="1:7">
-      <c r="A23" s="13" t="s">
+    <row r="23" s="18" customFormat="1" spans="1:7">
+      <c r="A23" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="F23" s="13" t="b">
+      <c r="F23" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="18" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" s="13" customFormat="1" spans="1:7">
-      <c r="B24" s="13" t="s">
+    <row r="24" s="18" customFormat="1" spans="1:7">
+      <c r="B24" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="18">
         <v>1883</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="18" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" s="13" customFormat="1" spans="1:7">
-      <c r="B25" s="13" t="s">
+    <row r="25" s="18" customFormat="1" spans="1:7">
+      <c r="B25" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" s="13" customFormat="1" spans="1:7">
-      <c r="B26" s="13" t="s">
+    <row r="26" s="18" customFormat="1" spans="1:7">
+      <c r="B26" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="18" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27" s="13" customFormat="1" spans="1:7">
-      <c r="B27" s="13" t="s">
+    <row r="27" s="18" customFormat="1" spans="1:7">
+      <c r="B27" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="18" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="28" s="13" customFormat="1" spans="1:7">
-      <c r="B28" s="13" t="s">
+    <row r="28" s="18" customFormat="1" spans="1:7">
+      <c r="B28" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="18" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2135,8 +2243,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.4" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="6.45736434108527" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.9302325581395" style="2" customWidth="1"/>
@@ -2216,6 +2324,342 @@
         <v>107</v>
       </c>
     </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2226,8 +2670,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.4" outlineLevelRow="4"/>
+  <dimension ref="A1:S29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.4"/>
   <cols>
     <col min="1" max="1" width="6.45736434108527" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.5968992248062" style="2" customWidth="1"/>
@@ -2253,16 +2697,16 @@
         <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>17</v>
@@ -2271,144 +2715,630 @@
         <v>21</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>119</v>
+        <v>139</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>102</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" s="4" customFormat="1" spans="1:19">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" s="4">
+        <v>60000</v>
+      </c>
+      <c r="G2" s="4">
+        <v>3000</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="I2" s="4">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="3" s="4" customFormat="1" spans="1:19">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F3" s="4">
+        <v>60000</v>
+      </c>
+      <c r="G3" s="4">
+        <v>3000</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I3" s="9">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="4" s="5" customFormat="1" spans="1:19">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2000</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2000</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" s="5" customFormat="1" spans="1:19">
+      <c r="A5" s="5">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" s="5" customFormat="1" spans="1:19">
+      <c r="A6" s="5">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" s="5" customFormat="1" spans="1:19">
+      <c r="A7" s="5">
+        <v>7</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J7" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" s="5" customFormat="1" spans="1:19">
+      <c r="A8" s="5">
+        <v>8</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J8" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" s="5" customFormat="1" spans="1:19">
+      <c r="A9" s="5">
+        <v>9</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J9" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" s="5" customFormat="1" spans="1:19">
+      <c r="A10" s="5">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J10" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" s="5" customFormat="1" spans="1:19">
+      <c r="A11" s="5">
+        <v>11</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J11" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" s="5" customFormat="1" spans="1:19">
+      <c r="A12" s="5">
+        <v>12</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J12" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" s="5" customFormat="1" spans="1:19">
+      <c r="A13" s="5">
+        <v>13</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J13" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" s="5" customFormat="1" spans="1:19">
+      <c r="A14" s="5">
+        <v>14</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="C14" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J14" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" s="5" customFormat="1" spans="1:19">
+      <c r="A15" s="5">
+        <v>15</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2" s="2">
+      <c r="C15" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J15" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" s="5" customFormat="1" spans="1:19">
+      <c r="A16" s="5">
+        <v>16</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J16" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" s="6" customFormat="1" spans="1:10">
+      <c r="A17" s="6">
+        <v>4</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F17" s="6">
+        <v>2000</v>
+      </c>
+      <c r="G17" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="18" s="6" customFormat="1" spans="1:10">
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="F2" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G2" s="2">
-        <v>3000</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="C18" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" s="6" customFormat="1" spans="1:10">
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="2">
-        <v>2404</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G3" s="2">
-        <v>3000</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="C19" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J19" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" s="6" customFormat="1" spans="1:10">
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I3" s="5">
-        <v>2404</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C20" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J20" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" s="6" customFormat="1" spans="1:10">
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="C21" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J21" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" s="6" customFormat="1" spans="1:10">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F4" s="2">
-        <v>2000</v>
-      </c>
-      <c r="G4" s="2">
-        <v>2000</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F5" s="2">
-        <v>2000</v>
-      </c>
-      <c r="G5" s="2">
-        <v>2000</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1</v>
+      <c r="C22" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J22" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" s="6" customFormat="1" spans="1:10">
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J23" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" s="6" customFormat="1" spans="1:10">
+      <c r="A24" s="6">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J24" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" s="6" customFormat="1" spans="1:10">
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J25" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" s="6" customFormat="1" spans="1:10">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J26" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" s="6" customFormat="1" spans="1:10">
+      <c r="A27" s="6">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J27" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" s="6" customFormat="1" spans="1:10">
+      <c r="A28" s="6">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J28" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" s="6" customFormat="1" spans="1:10">
+      <c r="A29" s="6">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J29" s="6">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2435,13 +3365,13 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>13</v>
